--- a/merged_cleaned.xlsx
+++ b/merged_cleaned.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,102 +433,102 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>CLIENT ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>COMMENCEMENT DATE</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>STAFF STRENGTH</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>SECTOR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>COUNTRY</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>PRESALES AND PARTNERSHIP</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>TECHNICAL EXPERTISE</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PROJECT DELIVERY</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>POST-SALES SUPPORT</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>NPS RATING</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>REVENUE</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>HARDWARE</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>SOFTWARE</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MANPOWER</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>GROSS PROFIT</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>GROSS MARGIN</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>NPS CATEGORY</t>
         </is>
@@ -533,7 +545,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>43849</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -607,7 +619,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>43849</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -681,7 +693,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>43849</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -755,7 +767,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>43849</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -829,7 +841,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>43849</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -903,7 +915,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>43970</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -977,7 +989,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>43970</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -1051,7 +1063,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>43970</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -1125,7 +1137,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>43970</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -1199,7 +1211,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>43970</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -1273,7 +1285,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>44395</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -1347,7 +1359,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>44395</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -1421,7 +1433,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>44395</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -1495,7 +1507,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>44395</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -1569,7 +1581,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>44395</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -1643,7 +1655,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -1717,7 +1729,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -1791,7 +1803,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -1865,7 +1877,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -1939,7 +1951,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -2013,7 +2025,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -2087,7 +2099,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -2161,7 +2173,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>45018</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -2235,7 +2247,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>45018</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -2309,7 +2321,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>45026</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -2383,7 +2395,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>45026</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -2457,7 +2469,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>45026</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -2531,7 +2543,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>45083</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -2605,7 +2617,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>45083</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -2679,7 +2691,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>45083</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -2753,7 +2765,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>45305</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -2827,7 +2839,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>45305</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -2901,7 +2913,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>45313</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -2975,7 +2987,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>45313</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -3049,7 +3061,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -3123,7 +3135,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -3197,7 +3209,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -3271,7 +3283,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -3345,7 +3357,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>45369</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -3419,7 +3431,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>45369</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -3493,7 +3505,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>45391</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -3567,7 +3579,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>45391</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -3641,7 +3653,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>45545</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -3715,7 +3727,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>45545</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -3789,7 +3801,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>45712</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -3863,7 +3875,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>45721</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -3937,7 +3949,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -4011,7 +4023,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44569</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -4085,7 +4097,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44569</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -4159,7 +4171,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44569</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -4233,7 +4245,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44569</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -4307,7 +4319,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>45307</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -4381,7 +4393,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>45307</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -4455,7 +4467,7 @@
           <t>Govt</t>
         </is>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>45741</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -4529,7 +4541,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>43645</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -4603,7 +4615,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>43645</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -4677,7 +4689,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>43645</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -4751,7 +4763,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>43645</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -4825,7 +4837,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>43645</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -4899,7 +4911,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>44334</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -4973,7 +4985,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>44334</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -5047,7 +5059,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>44334</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -5121,7 +5133,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>44334</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -5195,7 +5207,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>44334</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -5269,7 +5281,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>44772</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -5343,7 +5355,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>44772</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -5417,7 +5429,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>44772</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -5491,7 +5503,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>44772</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -5565,7 +5577,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>44942</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -5639,7 +5651,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>44942</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -5713,7 +5725,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>44942</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -5787,7 +5799,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>45093</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -5861,7 +5873,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="2" t="n">
         <v>45093</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -5935,7 +5947,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C75" s="1" t="n">
+      <c r="C75" s="2" t="n">
         <v>45093</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -6009,7 +6021,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C76" s="1" t="n">
+      <c r="C76" s="2" t="n">
         <v>45126</v>
       </c>
       <c r="D76" t="inlineStr">
@@ -6083,7 +6095,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C77" s="1" t="n">
+      <c r="C77" s="2" t="n">
         <v>45126</v>
       </c>
       <c r="D77" t="inlineStr">
@@ -6157,7 +6169,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C78" s="1" t="n">
+      <c r="C78" s="2" t="n">
         <v>45126</v>
       </c>
       <c r="D78" t="inlineStr">
@@ -6231,7 +6243,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C79" s="1" t="n">
+      <c r="C79" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="D79" t="inlineStr">
@@ -6305,7 +6317,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C80" s="1" t="n">
+      <c r="C80" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="D80" t="inlineStr">
@@ -6379,7 +6391,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C81" s="1" t="n">
+      <c r="C81" s="2" t="n">
         <v>45393</v>
       </c>
       <c r="D81" t="inlineStr">
@@ -6453,7 +6465,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C82" s="1" t="n">
+      <c r="C82" s="2" t="n">
         <v>45393</v>
       </c>
       <c r="D82" t="inlineStr">
@@ -6527,7 +6539,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C83" s="1" t="n">
+      <c r="C83" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="D83" t="inlineStr">
@@ -6601,7 +6613,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C84" s="1" t="n">
+      <c r="C84" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="D84" t="inlineStr">
@@ -6675,7 +6687,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C85" s="1" t="n">
+      <c r="C85" s="2" t="n">
         <v>45459</v>
       </c>
       <c r="D85" t="inlineStr">
@@ -6749,7 +6761,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C86" s="1" t="n">
+      <c r="C86" s="2" t="n">
         <v>45459</v>
       </c>
       <c r="D86" t="inlineStr">
@@ -6823,7 +6835,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C87" s="1" t="n">
+      <c r="C87" s="2" t="n">
         <v>45671</v>
       </c>
       <c r="D87" t="inlineStr">
@@ -6897,7 +6909,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C88" s="1" t="n">
+      <c r="C88" s="2" t="n">
         <v>45822</v>
       </c>
       <c r="D88" t="inlineStr">
@@ -6971,7 +6983,7 @@
           <t>NPO</t>
         </is>
       </c>
-      <c r="C89" s="1" t="n">
+      <c r="C89" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
@@ -7045,7 +7057,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C90" s="1" t="n">
+      <c r="C90" s="2" t="n">
         <v>43540</v>
       </c>
       <c r="D90" t="inlineStr">
@@ -7119,7 +7131,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C91" s="1" t="n">
+      <c r="C91" s="2" t="n">
         <v>43540</v>
       </c>
       <c r="D91" t="inlineStr">
@@ -7193,7 +7205,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C92" s="1" t="n">
+      <c r="C92" s="2" t="n">
         <v>43540</v>
       </c>
       <c r="D92" t="inlineStr">
@@ -7267,7 +7279,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C93" s="1" t="n">
+      <c r="C93" s="2" t="n">
         <v>43540</v>
       </c>
       <c r="D93" t="inlineStr">
@@ -7341,7 +7353,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C94" s="1" t="n">
+      <c r="C94" s="2" t="n">
         <v>43540</v>
       </c>
       <c r="D94" t="inlineStr">
@@ -7415,7 +7427,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C95" s="1" t="n">
+      <c r="C95" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="D95" t="inlineStr">
@@ -7489,7 +7501,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C96" s="1" t="n">
+      <c r="C96" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="D96" t="inlineStr">
@@ -7563,7 +7575,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C97" s="1" t="n">
+      <c r="C97" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="D97" t="inlineStr">
@@ -7637,7 +7649,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C98" s="1" t="n">
+      <c r="C98" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="D98" t="inlineStr">
@@ -7711,7 +7723,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C99" s="1" t="n">
+      <c r="C99" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="D99" t="inlineStr">
@@ -7785,7 +7797,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C100" s="1" t="n">
+      <c r="C100" s="2" t="n">
         <v>43613</v>
       </c>
       <c r="D100" t="inlineStr">
@@ -7859,7 +7871,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C101" s="1" t="n">
+      <c r="C101" s="2" t="n">
         <v>43613</v>
       </c>
       <c r="D101" t="inlineStr">
@@ -7933,7 +7945,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C102" s="1" t="n">
+      <c r="C102" s="2" t="n">
         <v>43613</v>
       </c>
       <c r="D102" t="inlineStr">
@@ -8007,7 +8019,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C103" s="1" t="n">
+      <c r="C103" s="2" t="n">
         <v>43613</v>
       </c>
       <c r="D103" t="inlineStr">
@@ -8081,7 +8093,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C104" s="1" t="n">
+      <c r="C104" s="2" t="n">
         <v>43613</v>
       </c>
       <c r="D104" t="inlineStr">
@@ -8155,7 +8167,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C105" s="1" t="n">
+      <c r="C105" s="2" t="n">
         <v>43859</v>
       </c>
       <c r="D105" t="inlineStr">
@@ -8229,7 +8241,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C106" s="1" t="n">
+      <c r="C106" s="2" t="n">
         <v>43859</v>
       </c>
       <c r="D106" t="inlineStr">
@@ -8303,7 +8315,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C107" s="1" t="n">
+      <c r="C107" s="2" t="n">
         <v>43859</v>
       </c>
       <c r="D107" t="inlineStr">
@@ -8377,7 +8389,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C108" s="1" t="n">
+      <c r="C108" s="2" t="n">
         <v>43859</v>
       </c>
       <c r="D108" t="inlineStr">
@@ -8451,7 +8463,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C109" s="1" t="n">
+      <c r="C109" s="2" t="n">
         <v>43859</v>
       </c>
       <c r="D109" t="inlineStr">
@@ -8525,7 +8537,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C110" s="1" t="n">
+      <c r="C110" s="2" t="n">
         <v>43909</v>
       </c>
       <c r="D110" t="inlineStr">
@@ -8599,7 +8611,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C111" s="1" t="n">
+      <c r="C111" s="2" t="n">
         <v>43909</v>
       </c>
       <c r="D111" t="inlineStr">
@@ -8673,7 +8685,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C112" s="1" t="n">
+      <c r="C112" s="2" t="n">
         <v>43909</v>
       </c>
       <c r="D112" t="inlineStr">
@@ -8747,7 +8759,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C113" s="1" t="n">
+      <c r="C113" s="2" t="n">
         <v>43909</v>
       </c>
       <c r="D113" t="inlineStr">
@@ -8821,7 +8833,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C114" s="1" t="n">
+      <c r="C114" s="2" t="n">
         <v>43909</v>
       </c>
       <c r="D114" t="inlineStr">
@@ -8895,7 +8907,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C115" s="1" t="n">
+      <c r="C115" s="2" t="n">
         <v>43909</v>
       </c>
       <c r="D115" t="inlineStr">
@@ -8969,7 +8981,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C116" s="1" t="n">
+      <c r="C116" s="2" t="n">
         <v>43909</v>
       </c>
       <c r="D116" t="inlineStr">
@@ -9043,7 +9055,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C117" s="1" t="n">
+      <c r="C117" s="2" t="n">
         <v>43909</v>
       </c>
       <c r="D117" t="inlineStr">
@@ -9117,7 +9129,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C118" s="1" t="n">
+      <c r="C118" s="2" t="n">
         <v>43909</v>
       </c>
       <c r="D118" t="inlineStr">
@@ -9191,7 +9203,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C119" s="1" t="n">
+      <c r="C119" s="2" t="n">
         <v>43909</v>
       </c>
       <c r="D119" t="inlineStr">
@@ -9265,7 +9277,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C120" s="1" t="n">
+      <c r="C120" s="2" t="n">
         <v>43980</v>
       </c>
       <c r="D120" t="inlineStr">
@@ -9339,7 +9351,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C121" s="1" t="n">
+      <c r="C121" s="2" t="n">
         <v>43980</v>
       </c>
       <c r="D121" t="inlineStr">
@@ -9413,7 +9425,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C122" s="1" t="n">
+      <c r="C122" s="2" t="n">
         <v>43980</v>
       </c>
       <c r="D122" t="inlineStr">
@@ -9487,7 +9499,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C123" s="1" t="n">
+      <c r="C123" s="2" t="n">
         <v>43980</v>
       </c>
       <c r="D123" t="inlineStr">
@@ -9561,7 +9573,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C124" s="1" t="n">
+      <c r="C124" s="2" t="n">
         <v>43980</v>
       </c>
       <c r="D124" t="inlineStr">
@@ -9635,7 +9647,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C125" s="1" t="n">
+      <c r="C125" s="2" t="n">
         <v>44017</v>
       </c>
       <c r="D125" t="inlineStr">
@@ -9709,7 +9721,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C126" s="1" t="n">
+      <c r="C126" s="2" t="n">
         <v>44017</v>
       </c>
       <c r="D126" t="inlineStr">
@@ -9783,7 +9795,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C127" s="1" t="n">
+      <c r="C127" s="2" t="n">
         <v>44017</v>
       </c>
       <c r="D127" t="inlineStr">
@@ -9857,7 +9869,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C128" s="1" t="n">
+      <c r="C128" s="2" t="n">
         <v>44017</v>
       </c>
       <c r="D128" t="inlineStr">
@@ -9931,7 +9943,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C129" s="1" t="n">
+      <c r="C129" s="2" t="n">
         <v>44017</v>
       </c>
       <c r="D129" t="inlineStr">
@@ -10005,7 +10017,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C130" s="1" t="n">
+      <c r="C130" s="2" t="n">
         <v>44031</v>
       </c>
       <c r="D130" t="inlineStr">
@@ -10079,7 +10091,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C131" s="1" t="n">
+      <c r="C131" s="2" t="n">
         <v>44031</v>
       </c>
       <c r="D131" t="inlineStr">
@@ -10153,7 +10165,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C132" s="1" t="n">
+      <c r="C132" s="2" t="n">
         <v>44031</v>
       </c>
       <c r="D132" t="inlineStr">
@@ -10227,7 +10239,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C133" s="1" t="n">
+      <c r="C133" s="2" t="n">
         <v>44031</v>
       </c>
       <c r="D133" t="inlineStr">
@@ -10301,7 +10313,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C134" s="1" t="n">
+      <c r="C134" s="2" t="n">
         <v>44031</v>
       </c>
       <c r="D134" t="inlineStr">
@@ -10375,7 +10387,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C135" s="1" t="n">
+      <c r="C135" s="2" t="n">
         <v>44093</v>
       </c>
       <c r="D135" t="inlineStr">
@@ -10449,7 +10461,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C136" s="1" t="n">
+      <c r="C136" s="2" t="n">
         <v>44093</v>
       </c>
       <c r="D136" t="inlineStr">
@@ -10523,7 +10535,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C137" s="1" t="n">
+      <c r="C137" s="2" t="n">
         <v>44093</v>
       </c>
       <c r="D137" t="inlineStr">
@@ -10597,7 +10609,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C138" s="1" t="n">
+      <c r="C138" s="2" t="n">
         <v>44093</v>
       </c>
       <c r="D138" t="inlineStr">
@@ -10671,7 +10683,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C139" s="1" t="n">
+      <c r="C139" s="2" t="n">
         <v>44093</v>
       </c>
       <c r="D139" t="inlineStr">
@@ -10745,7 +10757,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C140" s="1" t="n">
+      <c r="C140" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="D140" t="inlineStr">
@@ -10819,7 +10831,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C141" s="1" t="n">
+      <c r="C141" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="D141" t="inlineStr">
@@ -10893,7 +10905,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C142" s="1" t="n">
+      <c r="C142" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="D142" t="inlineStr">
@@ -10967,7 +10979,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C143" s="1" t="n">
+      <c r="C143" s="2" t="n">
         <v>44304</v>
       </c>
       <c r="D143" t="inlineStr">
@@ -11041,7 +11053,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C144" s="1" t="n">
+      <c r="C144" s="2" t="n">
         <v>44304</v>
       </c>
       <c r="D144" t="inlineStr">
@@ -11115,7 +11127,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C145" s="1" t="n">
+      <c r="C145" s="2" t="n">
         <v>44304</v>
       </c>
       <c r="D145" t="inlineStr">
@@ -11189,7 +11201,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C146" s="1" t="n">
+      <c r="C146" s="2" t="n">
         <v>44304</v>
       </c>
       <c r="D146" t="inlineStr">
@@ -11263,7 +11275,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C147" s="1" t="n">
+      <c r="C147" s="2" t="n">
         <v>44613</v>
       </c>
       <c r="D147" t="inlineStr">
@@ -11337,7 +11349,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C148" s="1" t="n">
+      <c r="C148" s="2" t="n">
         <v>44613</v>
       </c>
       <c r="D148" t="inlineStr">
@@ -11411,7 +11423,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C149" s="1" t="n">
+      <c r="C149" s="2" t="n">
         <v>44613</v>
       </c>
       <c r="D149" t="inlineStr">
@@ -11485,7 +11497,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C150" s="1" t="n">
+      <c r="C150" s="2" t="n">
         <v>44613</v>
       </c>
       <c r="D150" t="inlineStr">
@@ -11559,7 +11571,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C151" s="1" t="n">
+      <c r="C151" s="2" t="n">
         <v>44750</v>
       </c>
       <c r="D151" t="inlineStr">
@@ -11633,7 +11645,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C152" s="1" t="n">
+      <c r="C152" s="2" t="n">
         <v>44750</v>
       </c>
       <c r="D152" t="inlineStr">
@@ -11707,7 +11719,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C153" s="1" t="n">
+      <c r="C153" s="2" t="n">
         <v>44750</v>
       </c>
       <c r="D153" t="inlineStr">
@@ -11781,7 +11793,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C154" s="1" t="n">
+      <c r="C154" s="2" t="n">
         <v>44750</v>
       </c>
       <c r="D154" t="inlineStr">
@@ -11855,7 +11867,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C155" s="1" t="n">
+      <c r="C155" s="2" t="n">
         <v>44822</v>
       </c>
       <c r="D155" t="inlineStr">
@@ -11929,7 +11941,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C156" s="1" t="n">
+      <c r="C156" s="2" t="n">
         <v>44822</v>
       </c>
       <c r="D156" t="inlineStr">
@@ -12003,7 +12015,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C157" s="1" t="n">
+      <c r="C157" s="2" t="n">
         <v>44822</v>
       </c>
       <c r="D157" t="inlineStr">
@@ -12077,7 +12089,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C158" s="1" t="n">
+      <c r="C158" s="2" t="n">
         <v>44822</v>
       </c>
       <c r="D158" t="inlineStr">
@@ -12151,7 +12163,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C159" s="1" t="n">
+      <c r="C159" s="2" t="n">
         <v>44955</v>
       </c>
       <c r="D159" t="inlineStr">
@@ -12225,7 +12237,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C160" s="1" t="n">
+      <c r="C160" s="2" t="n">
         <v>44955</v>
       </c>
       <c r="D160" t="inlineStr">
@@ -12299,7 +12311,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C161" s="1" t="n">
+      <c r="C161" s="2" t="n">
         <v>44955</v>
       </c>
       <c r="D161" t="inlineStr">
@@ -12373,7 +12385,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C162" s="1" t="n">
+      <c r="C162" s="2" t="n">
         <v>44964</v>
       </c>
       <c r="D162" t="inlineStr">
@@ -12447,7 +12459,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C163" s="1" t="n">
+      <c r="C163" s="2" t="n">
         <v>44964</v>
       </c>
       <c r="D163" t="inlineStr">
@@ -12521,7 +12533,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C164" s="1" t="n">
+      <c r="C164" s="2" t="n">
         <v>44964</v>
       </c>
       <c r="D164" t="inlineStr">
@@ -12595,7 +12607,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C165" s="1" t="n">
+      <c r="C165" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="D165" t="inlineStr">
@@ -12669,7 +12681,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C166" s="1" t="n">
+      <c r="C166" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="D166" t="inlineStr">
@@ -12743,7 +12755,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C167" s="1" t="n">
+      <c r="C167" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="D167" t="inlineStr">
@@ -12817,7 +12829,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C168" s="1" t="n">
+      <c r="C168" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D168" t="inlineStr">
@@ -12891,7 +12903,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C169" s="1" t="n">
+      <c r="C169" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D169" t="inlineStr">
@@ -12965,7 +12977,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C170" s="1" t="n">
+      <c r="C170" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D170" t="inlineStr">
@@ -13039,7 +13051,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C171" s="1" t="n">
+      <c r="C171" s="2" t="n">
         <v>45054</v>
       </c>
       <c r="D171" t="inlineStr">
@@ -13113,7 +13125,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C172" s="1" t="n">
+      <c r="C172" s="2" t="n">
         <v>45054</v>
       </c>
       <c r="D172" t="inlineStr">
@@ -13187,7 +13199,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C173" s="1" t="n">
+      <c r="C173" s="2" t="n">
         <v>45054</v>
       </c>
       <c r="D173" t="inlineStr">
@@ -13261,7 +13273,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C174" s="1" t="n">
+      <c r="C174" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="D174" t="inlineStr">
@@ -13335,7 +13347,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C175" s="1" t="n">
+      <c r="C175" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="D175" t="inlineStr">
@@ -13409,7 +13421,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C176" s="1" t="n">
+      <c r="C176" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="D176" t="inlineStr">
@@ -13483,7 +13495,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C177" s="1" t="n">
+      <c r="C177" s="2" t="n">
         <v>45059</v>
       </c>
       <c r="D177" t="inlineStr">
@@ -13557,7 +13569,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C178" s="1" t="n">
+      <c r="C178" s="2" t="n">
         <v>45059</v>
       </c>
       <c r="D178" t="inlineStr">
@@ -13631,7 +13643,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C179" s="1" t="n">
+      <c r="C179" s="2" t="n">
         <v>45059</v>
       </c>
       <c r="D179" t="inlineStr">
@@ -13705,7 +13717,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C180" s="1" t="n">
+      <c r="C180" s="2" t="n">
         <v>45086</v>
       </c>
       <c r="D180" t="inlineStr">
@@ -13779,7 +13791,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C181" s="1" t="n">
+      <c r="C181" s="2" t="n">
         <v>45086</v>
       </c>
       <c r="D181" t="inlineStr">
@@ -13853,7 +13865,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C182" s="1" t="n">
+      <c r="C182" s="2" t="n">
         <v>45086</v>
       </c>
       <c r="D182" t="inlineStr">
@@ -13927,7 +13939,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C183" s="1" t="n">
+      <c r="C183" s="2" t="n">
         <v>45090</v>
       </c>
       <c r="D183" t="inlineStr">
@@ -14001,7 +14013,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C184" s="1" t="n">
+      <c r="C184" s="2" t="n">
         <v>45090</v>
       </c>
       <c r="D184" t="inlineStr">
@@ -14075,7 +14087,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C185" s="1" t="n">
+      <c r="C185" s="2" t="n">
         <v>45090</v>
       </c>
       <c r="D185" t="inlineStr">
@@ -14149,7 +14161,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C186" s="1" t="n">
+      <c r="C186" s="2" t="n">
         <v>45106</v>
       </c>
       <c r="D186" t="inlineStr">
@@ -14223,7 +14235,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C187" s="1" t="n">
+      <c r="C187" s="2" t="n">
         <v>45106</v>
       </c>
       <c r="D187" t="inlineStr">
@@ -14297,7 +14309,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C188" s="1" t="n">
+      <c r="C188" s="2" t="n">
         <v>45106</v>
       </c>
       <c r="D188" t="inlineStr">
@@ -14371,7 +14383,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C189" s="1" t="n">
+      <c r="C189" s="2" t="n">
         <v>45121</v>
       </c>
       <c r="D189" t="inlineStr">
@@ -14445,7 +14457,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C190" s="1" t="n">
+      <c r="C190" s="2" t="n">
         <v>45121</v>
       </c>
       <c r="D190" t="inlineStr">
@@ -14519,7 +14531,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C191" s="1" t="n">
+      <c r="C191" s="2" t="n">
         <v>45121</v>
       </c>
       <c r="D191" t="inlineStr">
@@ -14593,7 +14605,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C192" s="1" t="n">
+      <c r="C192" s="2" t="n">
         <v>45123</v>
       </c>
       <c r="D192" t="inlineStr">
@@ -14667,7 +14679,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C193" s="1" t="n">
+      <c r="C193" s="2" t="n">
         <v>45123</v>
       </c>
       <c r="D193" t="inlineStr">
@@ -14741,7 +14753,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C194" s="1" t="n">
+      <c r="C194" s="2" t="n">
         <v>45123</v>
       </c>
       <c r="D194" t="inlineStr">
@@ -14815,7 +14827,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C195" s="1" t="n">
+      <c r="C195" s="2" t="n">
         <v>45156</v>
       </c>
       <c r="D195" t="inlineStr">
@@ -14889,7 +14901,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C196" s="1" t="n">
+      <c r="C196" s="2" t="n">
         <v>45156</v>
       </c>
       <c r="D196" t="inlineStr">
@@ -14963,7 +14975,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C197" s="1" t="n">
+      <c r="C197" s="2" t="n">
         <v>45156</v>
       </c>
       <c r="D197" t="inlineStr">
@@ -15037,7 +15049,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C198" s="1" t="n">
+      <c r="C198" s="2" t="n">
         <v>45158</v>
       </c>
       <c r="D198" t="inlineStr">
@@ -15111,7 +15123,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C199" s="1" t="n">
+      <c r="C199" s="2" t="n">
         <v>45158</v>
       </c>
       <c r="D199" t="inlineStr">
@@ -15185,7 +15197,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C200" s="1" t="n">
+      <c r="C200" s="2" t="n">
         <v>45158</v>
       </c>
       <c r="D200" t="inlineStr">
@@ -15259,7 +15271,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C201" s="1" t="n">
+      <c r="C201" s="2" t="n">
         <v>45195</v>
       </c>
       <c r="D201" t="inlineStr">
@@ -15333,7 +15345,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C202" s="1" t="n">
+      <c r="C202" s="2" t="n">
         <v>45195</v>
       </c>
       <c r="D202" t="inlineStr">
@@ -15407,7 +15419,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C203" s="1" t="n">
+      <c r="C203" s="2" t="n">
         <v>45294</v>
       </c>
       <c r="D203" t="inlineStr">
@@ -15481,7 +15493,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C204" s="1" t="n">
+      <c r="C204" s="2" t="n">
         <v>45294</v>
       </c>
       <c r="D204" t="inlineStr">
@@ -15555,7 +15567,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C205" s="1" t="n">
+      <c r="C205" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="D205" t="inlineStr">
@@ -15629,7 +15641,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C206" s="1" t="n">
+      <c r="C206" s="2" t="n">
         <v>45304</v>
       </c>
       <c r="D206" t="inlineStr">
@@ -15703,7 +15715,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C207" s="1" t="n">
+      <c r="C207" s="2" t="n">
         <v>45304</v>
       </c>
       <c r="D207" t="inlineStr">
@@ -15777,7 +15789,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C208" s="1" t="n">
+      <c r="C208" s="2" t="n">
         <v>45311</v>
       </c>
       <c r="D208" t="inlineStr">
@@ -15851,7 +15863,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C209" s="1" t="n">
+      <c r="C209" s="2" t="n">
         <v>45311</v>
       </c>
       <c r="D209" t="inlineStr">
@@ -15925,7 +15937,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C210" s="1" t="n">
+      <c r="C210" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="D210" t="inlineStr">
@@ -15999,7 +16011,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C211" s="1" t="n">
+      <c r="C211" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="D211" t="inlineStr">
@@ -16073,7 +16085,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C212" s="1" t="n">
+      <c r="C212" s="2" t="n">
         <v>45374</v>
       </c>
       <c r="D212" t="inlineStr">
@@ -16147,7 +16159,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C213" s="1" t="n">
+      <c r="C213" s="2" t="n">
         <v>45374</v>
       </c>
       <c r="D213" t="inlineStr">
@@ -16221,7 +16233,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C214" s="1" t="n">
+      <c r="C214" s="2" t="n">
         <v>45392</v>
       </c>
       <c r="D214" t="inlineStr">
@@ -16295,7 +16307,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C215" s="1" t="n">
+      <c r="C215" s="2" t="n">
         <v>45392</v>
       </c>
       <c r="D215" t="inlineStr">
@@ -16369,7 +16381,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C216" s="1" t="n">
+      <c r="C216" s="2" t="n">
         <v>45435</v>
       </c>
       <c r="D216" t="inlineStr">
@@ -16443,7 +16455,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C217" s="1" t="n">
+      <c r="C217" s="2" t="n">
         <v>45435</v>
       </c>
       <c r="D217" t="inlineStr">
@@ -16517,7 +16529,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C218" s="1" t="n">
+      <c r="C218" s="2" t="n">
         <v>45441</v>
       </c>
       <c r="D218" t="inlineStr">
@@ -16591,7 +16603,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C219" s="1" t="n">
+      <c r="C219" s="2" t="n">
         <v>45441</v>
       </c>
       <c r="D219" t="inlineStr">
@@ -16665,7 +16677,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C220" s="1" t="n">
+      <c r="C220" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="D220" t="inlineStr">
@@ -16739,7 +16751,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C221" s="1" t="n">
+      <c r="C221" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="D221" t="inlineStr">
@@ -16813,7 +16825,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C222" s="1" t="n">
+      <c r="C222" s="2" t="n">
         <v>45466</v>
       </c>
       <c r="D222" t="inlineStr">
@@ -16887,7 +16899,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C223" s="1" t="n">
+      <c r="C223" s="2" t="n">
         <v>45466</v>
       </c>
       <c r="D223" t="inlineStr">
@@ -16961,7 +16973,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C224" s="1" t="n">
+      <c r="C224" s="2" t="n">
         <v>45489</v>
       </c>
       <c r="D224" t="inlineStr">
@@ -17035,7 +17047,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C225" s="1" t="n">
+      <c r="C225" s="2" t="n">
         <v>45489</v>
       </c>
       <c r="D225" t="inlineStr">
@@ -17109,7 +17121,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C226" s="1" t="n">
+      <c r="C226" s="2" t="n">
         <v>45490</v>
       </c>
       <c r="D226" t="inlineStr">
@@ -17183,7 +17195,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C227" s="1" t="n">
+      <c r="C227" s="2" t="n">
         <v>45490</v>
       </c>
       <c r="D227" t="inlineStr">
@@ -17257,7 +17269,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C228" s="1" t="n">
+      <c r="C228" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="D228" t="inlineStr">
@@ -17331,7 +17343,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C229" s="1" t="n">
+      <c r="C229" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="D229" t="inlineStr">
@@ -17405,7 +17417,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C230" s="1" t="n">
+      <c r="C230" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D230" t="inlineStr">
@@ -17479,7 +17491,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C231" s="1" t="n">
+      <c r="C231" s="2" t="n">
         <v>45718</v>
       </c>
       <c r="D231" t="inlineStr">
@@ -17553,7 +17565,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C232" s="1" t="n">
+      <c r="C232" s="2" t="n">
         <v>45720</v>
       </c>
       <c r="D232" t="inlineStr">
@@ -17627,7 +17639,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C233" s="1" t="n">
+      <c r="C233" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="D233" t="inlineStr">
@@ -17701,7 +17713,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C234" s="1" t="n">
+      <c r="C234" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="D234" t="inlineStr">
@@ -17775,7 +17787,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C235" s="1" t="n">
+      <c r="C235" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="D235" t="inlineStr">
@@ -17849,7 +17861,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C236" s="1" t="n">
+      <c r="C236" s="2" t="n">
         <v>45883</v>
       </c>
       <c r="D236" t="inlineStr">
@@ -17923,7 +17935,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C237" s="1" t="n">
+      <c r="C237" s="2" t="n">
         <v>43653</v>
       </c>
       <c r="D237" t="inlineStr">
@@ -17997,7 +18009,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C238" s="1" t="n">
+      <c r="C238" s="2" t="n">
         <v>43653</v>
       </c>
       <c r="D238" t="inlineStr">
@@ -18071,7 +18083,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C239" s="1" t="n">
+      <c r="C239" s="2" t="n">
         <v>43653</v>
       </c>
       <c r="D239" t="inlineStr">
@@ -18145,7 +18157,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C240" s="1" t="n">
+      <c r="C240" s="2" t="n">
         <v>43653</v>
       </c>
       <c r="D240" t="inlineStr">
@@ -18219,7 +18231,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C241" s="1" t="n">
+      <c r="C241" s="2" t="n">
         <v>43869</v>
       </c>
       <c r="D241" t="inlineStr">
@@ -18293,7 +18305,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C242" s="1" t="n">
+      <c r="C242" s="2" t="n">
         <v>43869</v>
       </c>
       <c r="D242" t="inlineStr">
@@ -18367,7 +18379,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C243" s="1" t="n">
+      <c r="C243" s="2" t="n">
         <v>43869</v>
       </c>
       <c r="D243" t="inlineStr">
@@ -18441,7 +18453,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C244" s="1" t="n">
+      <c r="C244" s="2" t="n">
         <v>43869</v>
       </c>
       <c r="D244" t="inlineStr">
@@ -18515,7 +18527,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C245" s="1" t="n">
+      <c r="C245" s="2" t="n">
         <v>43869</v>
       </c>
       <c r="D245" t="inlineStr">
@@ -18589,7 +18601,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C246" s="1" t="n">
+      <c r="C246" s="2" t="n">
         <v>44699</v>
       </c>
       <c r="D246" t="inlineStr">
@@ -18663,7 +18675,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C247" s="1" t="n">
+      <c r="C247" s="2" t="n">
         <v>44699</v>
       </c>
       <c r="D247" t="inlineStr">
@@ -18737,7 +18749,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C248" s="1" t="n">
+      <c r="C248" s="2" t="n">
         <v>44699</v>
       </c>
       <c r="D248" t="inlineStr">
@@ -18811,7 +18823,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C249" s="1" t="n">
+      <c r="C249" s="2" t="n">
         <v>44699</v>
       </c>
       <c r="D249" t="inlineStr">
@@ -18885,7 +18897,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C250" s="1" t="n">
+      <c r="C250" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="D250" t="inlineStr">
@@ -18959,7 +18971,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C251" s="1" t="n">
+      <c r="C251" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="D251" t="inlineStr">
@@ -19033,7 +19045,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C252" s="1" t="n">
+      <c r="C252" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="D252" t="inlineStr">
@@ -19107,7 +19119,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C253" s="1" t="n">
+      <c r="C253" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="D253" t="inlineStr">
@@ -19181,7 +19193,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C254" s="1" t="n">
+      <c r="C254" s="2" t="n">
         <v>44884</v>
       </c>
       <c r="D254" t="inlineStr">
@@ -19255,7 +19267,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C255" s="1" t="n">
+      <c r="C255" s="2" t="n">
         <v>44884</v>
       </c>
       <c r="D255" t="inlineStr">
@@ -19329,7 +19341,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C256" s="1" t="n">
+      <c r="C256" s="2" t="n">
         <v>44884</v>
       </c>
       <c r="D256" t="inlineStr">
@@ -19403,7 +19415,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C257" s="1" t="n">
+      <c r="C257" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="D257" t="inlineStr">
@@ -19477,7 +19489,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C258" s="1" t="n">
+      <c r="C258" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="D258" t="inlineStr">
@@ -19551,7 +19563,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C259" s="1" t="n">
+      <c r="C259" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="D259" t="inlineStr">
@@ -19625,7 +19637,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C260" s="1" t="n">
+      <c r="C260" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="D260" t="inlineStr">
@@ -19699,7 +19711,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C261" s="1" t="n">
+      <c r="C261" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="D261" t="inlineStr">
@@ -19773,7 +19785,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C262" s="1" t="n">
+      <c r="C262" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="D262" t="inlineStr">
@@ -19847,7 +19859,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C263" s="1" t="n">
+      <c r="C263" s="2" t="n">
         <v>45073</v>
       </c>
       <c r="D263" t="inlineStr">
@@ -19921,7 +19933,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C264" s="1" t="n">
+      <c r="C264" s="2" t="n">
         <v>45073</v>
       </c>
       <c r="D264" t="inlineStr">
@@ -19995,7 +20007,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C265" s="1" t="n">
+      <c r="C265" s="2" t="n">
         <v>45073</v>
       </c>
       <c r="D265" t="inlineStr">
@@ -20069,7 +20081,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C266" s="1" t="n">
+      <c r="C266" s="2" t="n">
         <v>45105</v>
       </c>
       <c r="D266" t="inlineStr">
@@ -20143,7 +20155,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C267" s="1" t="n">
+      <c r="C267" s="2" t="n">
         <v>45105</v>
       </c>
       <c r="D267" t="inlineStr">
@@ -20217,7 +20229,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C268" s="1" t="n">
+      <c r="C268" s="2" t="n">
         <v>45105</v>
       </c>
       <c r="D268" t="inlineStr">
@@ -20291,7 +20303,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C269" s="1" t="n">
+      <c r="C269" s="2" t="n">
         <v>45123</v>
       </c>
       <c r="D269" t="inlineStr">
@@ -20365,7 +20377,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C270" s="1" t="n">
+      <c r="C270" s="2" t="n">
         <v>45123</v>
       </c>
       <c r="D270" t="inlineStr">
@@ -20439,7 +20451,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C271" s="1" t="n">
+      <c r="C271" s="2" t="n">
         <v>45123</v>
       </c>
       <c r="D271" t="inlineStr">
@@ -20513,7 +20525,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C272" s="1" t="n">
+      <c r="C272" s="2" t="n">
         <v>45301</v>
       </c>
       <c r="D272" t="inlineStr">
@@ -20587,7 +20599,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C273" s="1" t="n">
+      <c r="C273" s="2" t="n">
         <v>45301</v>
       </c>
       <c r="D273" t="inlineStr">
@@ -20661,7 +20673,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C274" s="1" t="n">
+      <c r="C274" s="2" t="n">
         <v>45308</v>
       </c>
       <c r="D274" t="inlineStr">
@@ -20735,7 +20747,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C275" s="1" t="n">
+      <c r="C275" s="2" t="n">
         <v>45308</v>
       </c>
       <c r="D275" t="inlineStr">
@@ -20809,7 +20821,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C276" s="1" t="n">
+      <c r="C276" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="D276" t="inlineStr">
@@ -20883,7 +20895,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C277" s="1" t="n">
+      <c r="C277" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="D277" t="inlineStr">
@@ -20957,7 +20969,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C278" s="1" t="n">
+      <c r="C278" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="D278" t="inlineStr">
@@ -21031,7 +21043,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C279" s="1" t="n">
+      <c r="C279" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="D279" t="inlineStr">
@@ -21105,7 +21117,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C280" s="1" t="n">
+      <c r="C280" s="2" t="n">
         <v>45403</v>
       </c>
       <c r="D280" t="inlineStr">
@@ -21179,7 +21191,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C281" s="1" t="n">
+      <c r="C281" s="2" t="n">
         <v>45403</v>
       </c>
       <c r="D281" t="inlineStr">
@@ -21253,7 +21265,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C282" s="1" t="n">
+      <c r="C282" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="D282" t="inlineStr">
@@ -21327,7 +21339,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C283" s="1" t="n">
+      <c r="C283" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="D283" t="inlineStr">
@@ -21401,7 +21413,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C284" s="1" t="n">
+      <c r="C284" s="2" t="n">
         <v>45453</v>
       </c>
       <c r="D284" t="inlineStr">
@@ -21475,7 +21487,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C285" s="1" t="n">
+      <c r="C285" s="2" t="n">
         <v>45453</v>
       </c>
       <c r="D285" t="inlineStr">
@@ -21549,7 +21561,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C286" s="1" t="n">
+      <c r="C286" s="2" t="n">
         <v>45463</v>
       </c>
       <c r="D286" t="inlineStr">
@@ -21623,7 +21635,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C287" s="1" t="n">
+      <c r="C287" s="2" t="n">
         <v>45463</v>
       </c>
       <c r="D287" t="inlineStr">
@@ -21697,7 +21709,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C288" s="1" t="n">
+      <c r="C288" s="2" t="n">
         <v>45484</v>
       </c>
       <c r="D288" t="inlineStr">
@@ -21771,7 +21783,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C289" s="1" t="n">
+      <c r="C289" s="2" t="n">
         <v>45484</v>
       </c>
       <c r="D289" t="inlineStr">
@@ -21845,7 +21857,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C290" s="1" t="n">
+      <c r="C290" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D290" t="inlineStr">
@@ -21919,7 +21931,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C291" s="1" t="n">
+      <c r="C291" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D291" t="inlineStr">
@@ -21993,7 +22005,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C292" s="1" t="n">
+      <c r="C292" s="2" t="n">
         <v>45681</v>
       </c>
       <c r="D292" t="inlineStr">
@@ -22067,7 +22079,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C293" s="1" t="n">
+      <c r="C293" s="2" t="n">
         <v>45690</v>
       </c>
       <c r="D293" t="inlineStr">
@@ -22141,7 +22153,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C294" s="1" t="n">
+      <c r="C294" s="2" t="n">
         <v>45801</v>
       </c>
       <c r="D294" t="inlineStr">
@@ -22215,7 +22227,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C295" s="1" t="n">
+      <c r="C295" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="D295" t="inlineStr">
@@ -22289,7 +22301,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C296" s="1" t="n">
+      <c r="C296" s="2" t="n">
         <v>45841</v>
       </c>
       <c r="D296" t="inlineStr">
@@ -22363,7 +22375,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C297" s="1" t="n">
+      <c r="C297" s="2" t="n">
         <v>43474</v>
       </c>
       <c r="D297" t="inlineStr">
@@ -22437,7 +22449,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C298" s="1" t="n">
+      <c r="C298" s="2" t="n">
         <v>43474</v>
       </c>
       <c r="D298" t="inlineStr">
@@ -22511,7 +22523,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C299" s="1" t="n">
+      <c r="C299" s="2" t="n">
         <v>43474</v>
       </c>
       <c r="D299" t="inlineStr">
@@ -22585,7 +22597,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C300" s="1" t="n">
+      <c r="C300" s="2" t="n">
         <v>43474</v>
       </c>
       <c r="D300" t="inlineStr">
@@ -22659,7 +22671,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C301" s="1" t="n">
+      <c r="C301" s="2" t="n">
         <v>43474</v>
       </c>
       <c r="D301" t="inlineStr">
@@ -22733,7 +22745,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C302" s="1" t="n">
+      <c r="C302" s="2" t="n">
         <v>43563</v>
       </c>
       <c r="D302" t="inlineStr">
@@ -22807,7 +22819,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C303" s="1" t="n">
+      <c r="C303" s="2" t="n">
         <v>43563</v>
       </c>
       <c r="D303" t="inlineStr">
@@ -22881,7 +22893,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C304" s="1" t="n">
+      <c r="C304" s="2" t="n">
         <v>43563</v>
       </c>
       <c r="D304" t="inlineStr">
@@ -22955,7 +22967,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C305" s="1" t="n">
+      <c r="C305" s="2" t="n">
         <v>43563</v>
       </c>
       <c r="D305" t="inlineStr">
@@ -23029,7 +23041,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C306" s="1" t="n">
+      <c r="C306" s="2" t="n">
         <v>43563</v>
       </c>
       <c r="D306" t="inlineStr">
@@ -23103,7 +23115,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C307" s="1" t="n">
+      <c r="C307" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="D307" t="inlineStr">
@@ -23177,7 +23189,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C308" s="1" t="n">
+      <c r="C308" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="D308" t="inlineStr">
@@ -23251,7 +23263,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C309" s="1" t="n">
+      <c r="C309" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="D309" t="inlineStr">
@@ -23325,7 +23337,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C310" s="1" t="n">
+      <c r="C310" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="D310" t="inlineStr">
@@ -23399,7 +23411,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C311" s="1" t="n">
+      <c r="C311" s="2" t="n">
         <v>43604</v>
       </c>
       <c r="D311" t="inlineStr">
@@ -23473,7 +23485,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C312" s="1" t="n">
+      <c r="C312" s="2" t="n">
         <v>43604</v>
       </c>
       <c r="D312" t="inlineStr">
@@ -23547,7 +23559,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C313" s="1" t="n">
+      <c r="C313" s="2" t="n">
         <v>43695</v>
       </c>
       <c r="D313" t="inlineStr">
@@ -23621,7 +23633,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C314" s="1" t="n">
+      <c r="C314" s="2" t="n">
         <v>43695</v>
       </c>
       <c r="D314" t="inlineStr">
@@ -23695,7 +23707,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C315" s="1" t="n">
+      <c r="C315" s="2" t="n">
         <v>43695</v>
       </c>
       <c r="D315" t="inlineStr">
@@ -23769,7 +23781,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C316" s="1" t="n">
+      <c r="C316" s="2" t="n">
         <v>43695</v>
       </c>
       <c r="D316" t="inlineStr">
@@ -23843,7 +23855,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C317" s="1" t="n">
+      <c r="C317" s="2" t="n">
         <v>43695</v>
       </c>
       <c r="D317" t="inlineStr">
@@ -23917,7 +23929,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C318" s="1" t="n">
+      <c r="C318" s="2" t="n">
         <v>43755</v>
       </c>
       <c r="D318" t="inlineStr">
@@ -23991,7 +24003,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C319" s="1" t="n">
+      <c r="C319" s="2" t="n">
         <v>43755</v>
       </c>
       <c r="D319" t="inlineStr">
@@ -24065,7 +24077,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C320" s="1" t="n">
+      <c r="C320" s="2" t="n">
         <v>43755</v>
       </c>
       <c r="D320" t="inlineStr">
@@ -24139,7 +24151,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C321" s="1" t="n">
+      <c r="C321" s="2" t="n">
         <v>43755</v>
       </c>
       <c r="D321" t="inlineStr">
@@ -24213,7 +24225,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C322" s="1" t="n">
+      <c r="C322" s="2" t="n">
         <v>43755</v>
       </c>
       <c r="D322" t="inlineStr">
@@ -24287,7 +24299,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C323" s="1" t="n">
+      <c r="C323" s="2" t="n">
         <v>43848</v>
       </c>
       <c r="D323" t="inlineStr">
@@ -24361,7 +24373,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C324" s="1" t="n">
+      <c r="C324" s="2" t="n">
         <v>43848</v>
       </c>
       <c r="D324" t="inlineStr">
@@ -24435,7 +24447,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C325" s="1" t="n">
+      <c r="C325" s="2" t="n">
         <v>43848</v>
       </c>
       <c r="D325" t="inlineStr">
@@ -24509,7 +24521,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C326" s="1" t="n">
+      <c r="C326" s="2" t="n">
         <v>43848</v>
       </c>
       <c r="D326" t="inlineStr">
@@ -24583,7 +24595,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C327" s="1" t="n">
+      <c r="C327" s="2" t="n">
         <v>43848</v>
       </c>
       <c r="D327" t="inlineStr">
@@ -24657,7 +24669,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C328" s="1" t="n">
+      <c r="C328" s="2" t="n">
         <v>43930</v>
       </c>
       <c r="D328" t="inlineStr">
@@ -24731,7 +24743,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C329" s="1" t="n">
+      <c r="C329" s="2" t="n">
         <v>43930</v>
       </c>
       <c r="D329" t="inlineStr">
@@ -24805,7 +24817,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C330" s="1" t="n">
+      <c r="C330" s="2" t="n">
         <v>43930</v>
       </c>
       <c r="D330" t="inlineStr">
@@ -24879,7 +24891,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C331" s="1" t="n">
+      <c r="C331" s="2" t="n">
         <v>43930</v>
       </c>
       <c r="D331" t="inlineStr">
@@ -24953,7 +24965,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C332" s="1" t="n">
+      <c r="C332" s="2" t="n">
         <v>43930</v>
       </c>
       <c r="D332" t="inlineStr">
@@ -25027,7 +25039,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C333" s="1" t="n">
+      <c r="C333" s="2" t="n">
         <v>44123</v>
       </c>
       <c r="D333" t="inlineStr">
@@ -25101,7 +25113,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C334" s="1" t="n">
+      <c r="C334" s="2" t="n">
         <v>44123</v>
       </c>
       <c r="D334" t="inlineStr">
@@ -25175,7 +25187,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C335" s="1" t="n">
+      <c r="C335" s="2" t="n">
         <v>44123</v>
       </c>
       <c r="D335" t="inlineStr">
@@ -25249,7 +25261,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C336" s="1" t="n">
+      <c r="C336" s="2" t="n">
         <v>44123</v>
       </c>
       <c r="D336" t="inlineStr">
@@ -25323,7 +25335,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C337" s="1" t="n">
+      <c r="C337" s="2" t="n">
         <v>44123</v>
       </c>
       <c r="D337" t="inlineStr">
@@ -25397,7 +25409,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C338" s="1" t="n">
+      <c r="C338" s="2" t="n">
         <v>44205</v>
       </c>
       <c r="D338" t="inlineStr">
@@ -25471,7 +25483,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C339" s="1" t="n">
+      <c r="C339" s="2" t="n">
         <v>44205</v>
       </c>
       <c r="D339" t="inlineStr">
@@ -25545,7 +25557,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C340" s="1" t="n">
+      <c r="C340" s="2" t="n">
         <v>44205</v>
       </c>
       <c r="D340" t="inlineStr">
@@ -25619,7 +25631,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C341" s="1" t="n">
+      <c r="C341" s="2" t="n">
         <v>44205</v>
       </c>
       <c r="D341" t="inlineStr">
@@ -25693,7 +25705,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C342" s="1" t="n">
+      <c r="C342" s="2" t="n">
         <v>44205</v>
       </c>
       <c r="D342" t="inlineStr">
@@ -25767,7 +25779,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C343" s="1" t="n">
+      <c r="C343" s="2" t="n">
         <v>44339</v>
       </c>
       <c r="D343" t="inlineStr">
@@ -25841,7 +25853,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C344" s="1" t="n">
+      <c r="C344" s="2" t="n">
         <v>44339</v>
       </c>
       <c r="D344" t="inlineStr">
@@ -25915,7 +25927,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C345" s="1" t="n">
+      <c r="C345" s="2" t="n">
         <v>44339</v>
       </c>
       <c r="D345" t="inlineStr">
@@ -25989,7 +26001,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C346" s="1" t="n">
+      <c r="C346" s="2" t="n">
         <v>44339</v>
       </c>
       <c r="D346" t="inlineStr">
@@ -26063,7 +26075,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C347" s="1" t="n">
+      <c r="C347" s="2" t="n">
         <v>44339</v>
       </c>
       <c r="D347" t="inlineStr">
@@ -26137,7 +26149,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C348" s="1" t="n">
+      <c r="C348" s="2" t="n">
         <v>44669</v>
       </c>
       <c r="D348" t="inlineStr">
@@ -26211,7 +26223,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C349" s="1" t="n">
+      <c r="C349" s="2" t="n">
         <v>44669</v>
       </c>
       <c r="D349" t="inlineStr">
@@ -26285,7 +26297,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C350" s="1" t="n">
+      <c r="C350" s="2" t="n">
         <v>44669</v>
       </c>
       <c r="D350" t="inlineStr">
@@ -26359,7 +26371,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C351" s="1" t="n">
+      <c r="C351" s="2" t="n">
         <v>44669</v>
       </c>
       <c r="D351" t="inlineStr">
@@ -26433,7 +26445,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C352" s="1" t="n">
+      <c r="C352" s="2" t="n">
         <v>44720</v>
       </c>
       <c r="D352" t="inlineStr">
@@ -26507,7 +26519,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C353" s="1" t="n">
+      <c r="C353" s="2" t="n">
         <v>44720</v>
       </c>
       <c r="D353" t="inlineStr">
@@ -26581,7 +26593,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C354" s="1" t="n">
+      <c r="C354" s="2" t="n">
         <v>44720</v>
       </c>
       <c r="D354" t="inlineStr">
@@ -26655,7 +26667,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C355" s="1" t="n">
+      <c r="C355" s="2" t="n">
         <v>44720</v>
       </c>
       <c r="D355" t="inlineStr">
@@ -26729,7 +26741,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C356" s="1" t="n">
+      <c r="C356" s="2" t="n">
         <v>44733</v>
       </c>
       <c r="D356" t="inlineStr">
@@ -26803,7 +26815,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C357" s="1" t="n">
+      <c r="C357" s="2" t="n">
         <v>44733</v>
       </c>
       <c r="D357" t="inlineStr">
@@ -26877,7 +26889,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C358" s="1" t="n">
+      <c r="C358" s="2" t="n">
         <v>44733</v>
       </c>
       <c r="D358" t="inlineStr">
@@ -26951,7 +26963,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C359" s="1" t="n">
+      <c r="C359" s="2" t="n">
         <v>44733</v>
       </c>
       <c r="D359" t="inlineStr">
@@ -27025,7 +27037,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C360" s="1" t="n">
+      <c r="C360" s="2" t="n">
         <v>44759</v>
       </c>
       <c r="D360" t="inlineStr">
@@ -27099,7 +27111,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C361" s="1" t="n">
+      <c r="C361" s="2" t="n">
         <v>44759</v>
       </c>
       <c r="D361" t="inlineStr">
@@ -27173,7 +27185,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C362" s="1" t="n">
+      <c r="C362" s="2" t="n">
         <v>44759</v>
       </c>
       <c r="D362" t="inlineStr">
@@ -27247,7 +27259,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C363" s="1" t="n">
+      <c r="C363" s="2" t="n">
         <v>44759</v>
       </c>
       <c r="D363" t="inlineStr">
@@ -27321,7 +27333,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C364" s="1" t="n">
+      <c r="C364" s="2" t="n">
         <v>44987</v>
       </c>
       <c r="D364" t="inlineStr">
@@ -27395,7 +27407,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C365" s="1" t="n">
+      <c r="C365" s="2" t="n">
         <v>44987</v>
       </c>
       <c r="D365" t="inlineStr">
@@ -27469,7 +27481,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C366" s="1" t="n">
+      <c r="C366" s="2" t="n">
         <v>44987</v>
       </c>
       <c r="D366" t="inlineStr">
@@ -27543,7 +27555,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C367" s="1" t="n">
+      <c r="C367" s="2" t="n">
         <v>45004</v>
       </c>
       <c r="D367" t="inlineStr">
@@ -27617,7 +27629,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C368" s="1" t="n">
+      <c r="C368" s="2" t="n">
         <v>45004</v>
       </c>
       <c r="D368" t="inlineStr">
@@ -27691,7 +27703,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C369" s="1" t="n">
+      <c r="C369" s="2" t="n">
         <v>45004</v>
       </c>
       <c r="D369" t="inlineStr">
@@ -27765,7 +27777,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C370" s="1" t="n">
+      <c r="C370" s="2" t="n">
         <v>45022</v>
       </c>
       <c r="D370" t="inlineStr">
@@ -27839,7 +27851,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C371" s="1" t="n">
+      <c r="C371" s="2" t="n">
         <v>45022</v>
       </c>
       <c r="D371" t="inlineStr">
@@ -27913,7 +27925,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C372" s="1" t="n">
+      <c r="C372" s="2" t="n">
         <v>45022</v>
       </c>
       <c r="D372" t="inlineStr">
@@ -27987,7 +27999,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C373" s="1" t="n">
+      <c r="C373" s="2" t="n">
         <v>45032</v>
       </c>
       <c r="D373" t="inlineStr">
@@ -28061,7 +28073,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C374" s="1" t="n">
+      <c r="C374" s="2" t="n">
         <v>45032</v>
       </c>
       <c r="D374" t="inlineStr">
@@ -28135,7 +28147,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C375" s="1" t="n">
+      <c r="C375" s="2" t="n">
         <v>45032</v>
       </c>
       <c r="D375" t="inlineStr">
@@ -28209,7 +28221,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C376" s="1" t="n">
+      <c r="C376" s="2" t="n">
         <v>45062</v>
       </c>
       <c r="D376" t="inlineStr">
@@ -28283,7 +28295,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C377" s="1" t="n">
+      <c r="C377" s="2" t="n">
         <v>45062</v>
       </c>
       <c r="D377" t="inlineStr">
@@ -28357,7 +28369,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C378" s="1" t="n">
+      <c r="C378" s="2" t="n">
         <v>45062</v>
       </c>
       <c r="D378" t="inlineStr">
@@ -28431,7 +28443,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C379" s="1" t="n">
+      <c r="C379" s="2" t="n">
         <v>45310</v>
       </c>
       <c r="D379" t="inlineStr">
@@ -28505,7 +28517,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C380" s="1" t="n">
+      <c r="C380" s="2" t="n">
         <v>45310</v>
       </c>
       <c r="D380" t="inlineStr">
@@ -28579,7 +28591,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C381" s="1" t="n">
+      <c r="C381" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="D381" t="inlineStr">
@@ -28653,7 +28665,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C382" s="1" t="n">
+      <c r="C382" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="D382" t="inlineStr">
@@ -28727,7 +28739,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C383" s="1" t="n">
+      <c r="C383" s="2" t="n">
         <v>45449</v>
       </c>
       <c r="D383" t="inlineStr">
@@ -28801,7 +28813,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C384" s="1" t="n">
+      <c r="C384" s="2" t="n">
         <v>45449</v>
       </c>
       <c r="D384" t="inlineStr">
@@ -28875,7 +28887,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C385" s="1" t="n">
+      <c r="C385" s="2" t="n">
         <v>45459</v>
       </c>
       <c r="D385" t="inlineStr">
@@ -28949,7 +28961,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C386" s="1" t="n">
+      <c r="C386" s="2" t="n">
         <v>45459</v>
       </c>
       <c r="D386" t="inlineStr">
@@ -29023,7 +29035,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C387" s="1" t="n">
+      <c r="C387" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="D387" t="inlineStr">
@@ -29097,7 +29109,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C388" s="1" t="n">
+      <c r="C388" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="D388" t="inlineStr">
@@ -29171,7 +29183,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C389" s="1" t="n">
+      <c r="C389" s="2" t="n">
         <v>45661</v>
       </c>
       <c r="D389" t="inlineStr">
@@ -29245,7 +29257,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C390" s="1" t="n">
+      <c r="C390" s="2" t="n">
         <v>45671</v>
       </c>
       <c r="D390" t="inlineStr">
@@ -29319,7 +29331,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C391" s="1" t="n">
+      <c r="C391" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="D391" t="inlineStr">
@@ -29393,7 +29405,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C392" s="1" t="n">
+      <c r="C392" s="2" t="n">
         <v>45781</v>
       </c>
       <c r="D392" t="inlineStr">
@@ -29467,7 +29479,7 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="C393" s="1" t="n">
+      <c r="C393" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="D393" t="inlineStr">
